--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501719</v>
       </c>
       <c r="B2" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501720</v>
       </c>
       <c r="B3" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501719</v>
       </c>
       <c r="B2" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501720</v>
       </c>
       <c r="B3" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501719</v>
       </c>
       <c r="B2" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501720</v>
       </c>
       <c r="B3" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501719</v>
       </c>
       <c r="B2" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501720</v>
       </c>
       <c r="B3" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501719</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501720</v>
       </c>
       <c r="B3" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37151-2026 artfynd.xlsx
+++ b/artfynd/A 37151-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136501718</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
